--- a/cfg/excel/RoleAttributeCfg.xlsx
+++ b/cfg/excel/RoleAttributeCfg.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="3"/>
+    <workbookView windowHeight="16995" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="AttributeRole" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="169">
   <si>
     <t>##var</t>
   </si>
@@ -280,6 +280,9 @@
     <t>(list#sep=,),SkillBase</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>技能强化提升</t>
   </si>
   <si>
@@ -289,6 +292,9 @@
     <t>1,3</t>
   </si>
   <si>
+    <t>女警主动技能，冷却时间，技能范围，持续时间</t>
+  </si>
+  <si>
     <t>CDSkill_20,AreaSkill_500,TimeSkill_5</t>
   </si>
   <si>
@@ -340,6 +346,9 @@
     <t>CDSkill_-1,AreaSkill_35,TimeSkill_0.6</t>
   </si>
   <si>
+    <t>白袍主动技能，冷却时间，技能伤害</t>
+  </si>
+  <si>
     <t>CDSkill_20,DamageSkill_75</t>
   </si>
   <si>
@@ -355,16 +364,19 @@
     <t>CDSkill_-0.5,DamageSkill_10</t>
   </si>
   <si>
-    <t>CDSkill_17,DamageSkill_105</t>
+    <t>CDSkill_17,DamageSkill_115</t>
   </si>
   <si>
     <t>CDSkill_-0.5,DamageSkill_15</t>
   </si>
   <si>
-    <t>CDSkill_16.5,DamageSkill_120</t>
-  </si>
-  <si>
-    <t>CDSkill_16,DamageSkill_135</t>
+    <t>CDSkill_16.5,DamageSkill_130</t>
+  </si>
+  <si>
+    <t>CDSkill_16,DamageSkill_145</t>
+  </si>
+  <si>
+    <t>山主动技能，冷却时间，技能伤害</t>
   </si>
   <si>
     <t>CDSkill_25,DamageSkill_30</t>
@@ -388,6 +400,9 @@
     <t>CDSkill_-1,DamageSkill_15</t>
   </si>
   <si>
+    <t>女警被动技能，技能效果，持续时间</t>
+  </si>
+  <si>
     <t>MagnificationSkill_10,TimeSkill_3</t>
   </si>
   <si>
@@ -421,6 +436,9 @@
     <t>MagnificationSkill_5,TimeSkill_0.7</t>
   </si>
   <si>
+    <t>白袍被动技能，技能效果</t>
+  </si>
+  <si>
     <t>MagnificationSkill_10</t>
   </si>
   <si>
@@ -451,6 +469,9 @@
     <t>MagnificationSkill_8</t>
   </si>
   <si>
+    <t>山被动技能，技能效果</t>
+  </si>
+  <si>
     <t>MagnificationSkill_4</t>
   </si>
   <si>
@@ -463,31 +484,22 @@
     <t>MagnificationSkill_7</t>
   </si>
   <si>
-    <t>DamageSkill_2</t>
-  </si>
-  <si>
-    <t>DamageSkill_1</t>
-  </si>
-  <si>
-    <t>DamageSkill_4</t>
-  </si>
-  <si>
-    <t>DamageSkill_6</t>
-  </si>
-  <si>
-    <t>DamageSkill_10</t>
-  </si>
-  <si>
-    <t>DamageSkill_12</t>
-  </si>
-  <si>
-    <t>DamageSkill_3</t>
-  </si>
-  <si>
-    <t>DamageSkill_15</t>
-  </si>
-  <si>
-    <t>DamageSkill_5</t>
+    <t>女警被动技能，技能效果</t>
+  </si>
+  <si>
+    <t>MagnificationSkill_1</t>
+  </si>
+  <si>
+    <t>MagnificationSkill_6</t>
+  </si>
+  <si>
+    <t>MagnificationSkill_12</t>
+  </si>
+  <si>
+    <t>MagnificationSkill_15</t>
+  </si>
+  <si>
+    <t>白袍被动技能，技能效果，持续时间</t>
   </si>
   <si>
     <t>MagnificationSkill_5,TimeSkill_0.5</t>
@@ -10781,21 +10793,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BD57"/>
+  <dimension ref="A1:BE57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="11.375"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="23.25" customWidth="1"/>
     <col min="5" max="5" width="18.375" customWidth="1"/>
-    <col min="6" max="6" width="43.8083333333333" customWidth="1"/>
-    <col min="7" max="7" width="24.25" customWidth="1"/>
-    <col min="8" max="8" width="50.8666666666667" customWidth="1"/>
-    <col min="9" max="9" width="16.5" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="6" max="6" width="49.45" customWidth="1"/>
+    <col min="7" max="7" width="43.8083333333333" customWidth="1"/>
+    <col min="8" max="8" width="24.25" customWidth="1"/>
+    <col min="9" max="9" width="50.8666666666667" customWidth="1"/>
+    <col min="10" max="10" width="16.5" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:56">
+    <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:57">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -10811,18 +10824,19 @@
       <c r="E1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="5"/>
+      <c r="G1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:56">
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:57">
       <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
@@ -10838,18 +10852,19 @@
       <c r="E2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="7"/>
+      <c r="G2" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" s="3" customFormat="1" ht="20.25" spans="1:56">
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="20.25" spans="1:57">
       <c r="A3" s="9" t="s">
         <v>36</v>
       </c>
@@ -10868,21 +10883,24 @@
       <c r="F3" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I3" s="9"/>
+      <c r="I3" s="9" t="s">
+        <v>83</v>
+      </c>
       <c r="J3" s="9"/>
-    </row>
-    <row r="4" ht="20.25" spans="1:56">
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" ht="20.25" spans="1:57">
       <c r="B4" s="11">
         <v>1001005</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D4" s="11">
         <v>7</v>
@@ -10891,15 +10909,17 @@
         <v>10</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="11">
+        <v>85</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="11">
         <v>10</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="I4" s="12"/>
+      <c r="I4" s="11" t="s">
+        <v>87</v>
+      </c>
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
@@ -10947,13 +10967,14 @@
       <c r="BB4" s="12"/>
       <c r="BC4" s="12"/>
       <c r="BD4" s="12"/>
-    </row>
-    <row r="5" ht="20.25" spans="1:56">
+      <c r="BE4" s="12"/>
+    </row>
+    <row r="5" ht="20.25" spans="1:57">
       <c r="B5" s="11">
         <v>1002005</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D5" s="11">
         <v>7</v>
@@ -10961,16 +10982,16 @@
       <c r="E5" s="11">
         <v>35</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="F5" s="11"/>
+      <c r="G5" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="11">
         <v>15</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I5" s="12"/>
+      <c r="I5" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
       <c r="L5" s="12"/>
@@ -11018,13 +11039,14 @@
       <c r="BB5" s="12"/>
       <c r="BC5" s="12"/>
       <c r="BD5" s="12"/>
-    </row>
-    <row r="6" ht="20.25" spans="1:56">
+      <c r="BE5" s="12"/>
+    </row>
+    <row r="6" ht="20.25" spans="1:57">
       <c r="B6" s="11">
         <v>1003005</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" s="11">
         <v>7</v>
@@ -11032,16 +11054,16 @@
       <c r="E6" s="11">
         <v>70</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="11">
+      <c r="F6" s="11"/>
+      <c r="G6" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" s="11">
         <v>20</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="12"/>
+      <c r="I6" s="11" t="s">
+        <v>93</v>
+      </c>
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
       <c r="L6" s="12"/>
@@ -11089,13 +11111,14 @@
       <c r="BB6" s="12"/>
       <c r="BC6" s="12"/>
       <c r="BD6" s="12"/>
-    </row>
-    <row r="7" ht="20.25" spans="1:56">
+      <c r="BE6" s="12"/>
+    </row>
+    <row r="7" ht="20.25" spans="1:57">
       <c r="B7" s="11">
         <v>1004005</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D7" s="11">
         <v>7</v>
@@ -11103,16 +11126,16 @@
       <c r="E7" s="11">
         <v>135</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" s="11">
-        <v>0</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="I7" s="12"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
       <c r="L7" s="12"/>
@@ -11160,13 +11183,14 @@
       <c r="BB7" s="12"/>
       <c r="BC7" s="12"/>
       <c r="BD7" s="12"/>
-    </row>
-    <row r="8" ht="20.25" spans="1:56">
+      <c r="BE7" s="12"/>
+    </row>
+    <row r="8" ht="20.25" spans="1:57">
       <c r="B8" s="11">
         <v>1005005</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D8" s="11">
         <v>7</v>
@@ -11174,16 +11198,16 @@
       <c r="E8" s="11">
         <v>165</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G8" s="11">
-        <v>0</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="I8" s="12"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>99</v>
+      </c>
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
       <c r="L8" s="12"/>
@@ -11231,13 +11255,14 @@
       <c r="BB8" s="12"/>
       <c r="BC8" s="12"/>
       <c r="BD8" s="12"/>
-    </row>
-    <row r="9" ht="20.25" spans="1:56">
+      <c r="BE8" s="12"/>
+    </row>
+    <row r="9" ht="20.25" spans="1:57">
       <c r="B9" s="11">
         <v>1006005</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D9" s="11">
         <v>7</v>
@@ -11245,16 +11270,16 @@
       <c r="E9" s="11">
         <v>200</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="G9" s="11">
-        <v>0</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="I9" s="12"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>102</v>
+      </c>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
@@ -11302,13 +11327,14 @@
       <c r="BB9" s="12"/>
       <c r="BC9" s="12"/>
       <c r="BD9" s="12"/>
-    </row>
-    <row r="10" ht="20.25" spans="1:56">
+      <c r="BE9" s="12"/>
+    </row>
+    <row r="10" ht="20.25" spans="1:57">
       <c r="B10" s="11">
         <v>2001005</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" s="11">
         <v>7</v>
@@ -11317,15 +11343,17 @@
         <v>10</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G10" s="11">
+        <v>103</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="11">
         <v>10</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="I10" s="12"/>
+      <c r="I10" s="11" t="s">
+        <v>105</v>
+      </c>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
       <c r="L10" s="12"/>
@@ -11373,13 +11401,14 @@
       <c r="BB10" s="12"/>
       <c r="BC10" s="12"/>
       <c r="BD10" s="12"/>
-    </row>
-    <row r="11" ht="20.25" spans="1:56">
+      <c r="BE10" s="12"/>
+    </row>
+    <row r="11" ht="20.25" spans="1:57">
       <c r="B11" s="11">
         <v>2002005</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D11" s="11">
         <v>7</v>
@@ -11387,16 +11416,16 @@
       <c r="E11" s="11">
         <v>35</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G11" s="11">
+      <c r="F11" s="11"/>
+      <c r="G11" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="11">
         <v>15</v>
       </c>
-      <c r="H11" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="12"/>
+      <c r="I11" s="11" t="s">
+        <v>105</v>
+      </c>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
       <c r="L11" s="12"/>
@@ -11444,13 +11473,14 @@
       <c r="BB11" s="12"/>
       <c r="BC11" s="12"/>
       <c r="BD11" s="12"/>
-    </row>
-    <row r="12" ht="20.25" spans="1:56">
+      <c r="BE11" s="12"/>
+    </row>
+    <row r="12" ht="20.25" spans="1:57">
       <c r="B12" s="11">
         <v>2003005</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D12" s="11">
         <v>7</v>
@@ -11458,16 +11488,16 @@
       <c r="E12" s="11">
         <v>70</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="11">
+      <c r="F12" s="11"/>
+      <c r="G12" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="11">
         <v>20</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="I12" s="12"/>
+      <c r="I12" s="11" t="s">
+        <v>108</v>
+      </c>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
       <c r="L12" s="12"/>
@@ -11515,13 +11545,14 @@
       <c r="BB12" s="12"/>
       <c r="BC12" s="12"/>
       <c r="BD12" s="12"/>
-    </row>
-    <row r="13" ht="20.25" spans="1:56">
+      <c r="BE12" s="12"/>
+    </row>
+    <row r="13" ht="20.25" spans="1:57">
       <c r="B13" s="11">
         <v>2004005</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" s="11">
         <v>7</v>
@@ -11529,16 +11560,16 @@
       <c r="E13" s="11">
         <v>135</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="G13" s="11">
-        <v>0</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I13" s="12"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>110</v>
+      </c>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
       <c r="L13" s="12"/>
@@ -11586,13 +11617,14 @@
       <c r="BB13" s="12"/>
       <c r="BC13" s="12"/>
       <c r="BD13" s="12"/>
-    </row>
-    <row r="14" ht="20.25" spans="1:56">
+      <c r="BE13" s="12"/>
+    </row>
+    <row r="14" ht="20.25" spans="1:57">
       <c r="B14" s="11">
         <v>2005005</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D14" s="11">
         <v>7</v>
@@ -11600,16 +11632,16 @@
       <c r="E14" s="11">
         <v>165</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G14" s="11">
-        <v>0</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I14" s="12"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>110</v>
+      </c>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
       <c r="L14" s="12"/>
@@ -11657,13 +11689,14 @@
       <c r="BB14" s="12"/>
       <c r="BC14" s="12"/>
       <c r="BD14" s="12"/>
-    </row>
-    <row r="15" ht="20.25" spans="1:56">
+      <c r="BE14" s="12"/>
+    </row>
+    <row r="15" ht="20.25" spans="1:57">
       <c r="B15" s="11">
         <v>2006005</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D15" s="11">
         <v>7</v>
@@ -11671,16 +11704,16 @@
       <c r="E15" s="11">
         <v>200</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" s="11">
-        <v>0</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I15" s="12"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" s="11">
+        <v>0</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>110</v>
+      </c>
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
@@ -11728,13 +11761,14 @@
       <c r="BB15" s="12"/>
       <c r="BC15" s="12"/>
       <c r="BD15" s="12"/>
-    </row>
-    <row r="16" ht="20.25" spans="1:56">
+      <c r="BE15" s="12"/>
+    </row>
+    <row r="16" ht="20.25" spans="1:57">
       <c r="B16" s="11">
         <v>3001005</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D16" s="11">
         <v>7</v>
@@ -11743,15 +11777,17 @@
         <v>10</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" s="11">
+        <v>113</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="11">
         <v>10</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="I16" s="12"/>
+      <c r="I16" s="11" t="s">
+        <v>105</v>
+      </c>
       <c r="J16" s="12"/>
       <c r="K16" s="12"/>
       <c r="L16" s="12"/>
@@ -11799,13 +11835,14 @@
       <c r="BB16" s="12"/>
       <c r="BC16" s="12"/>
       <c r="BD16" s="12"/>
-    </row>
-    <row r="17" ht="20.25" spans="2:56">
+      <c r="BE16" s="12"/>
+    </row>
+    <row r="17" ht="20.25" spans="2:57">
       <c r="B17" s="11">
         <v>3002005</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" s="11">
         <v>7</v>
@@ -11813,16 +11850,16 @@
       <c r="E17" s="11">
         <v>35</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="G17" s="11">
+      <c r="F17" s="11"/>
+      <c r="G17" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" s="11">
         <v>15</v>
       </c>
-      <c r="H17" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="I17" s="12"/>
+      <c r="I17" s="11" t="s">
+        <v>105</v>
+      </c>
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
       <c r="L17" s="12"/>
@@ -11870,13 +11907,14 @@
       <c r="BB17" s="12"/>
       <c r="BC17" s="12"/>
       <c r="BD17" s="12"/>
-    </row>
-    <row r="18" ht="20.25" spans="2:56">
+      <c r="BE17" s="12"/>
+    </row>
+    <row r="18" ht="20.25" spans="2:57">
       <c r="B18" s="11">
         <v>3003005</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D18" s="11">
         <v>7</v>
@@ -11884,16 +11922,16 @@
       <c r="E18" s="11">
         <v>70</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="11">
+      <c r="F18" s="11"/>
+      <c r="G18" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18" s="11">
         <v>20</v>
       </c>
-      <c r="H18" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="I18" s="12"/>
+      <c r="I18" s="11" t="s">
+        <v>108</v>
+      </c>
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
@@ -11941,13 +11979,14 @@
       <c r="BB18" s="12"/>
       <c r="BC18" s="12"/>
       <c r="BD18" s="12"/>
-    </row>
-    <row r="19" ht="20.25" spans="2:56">
+      <c r="BE18" s="12"/>
+    </row>
+    <row r="19" ht="20.25" spans="2:57">
       <c r="B19" s="11">
         <v>3004005</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D19" s="11">
         <v>7</v>
@@ -11955,16 +11994,16 @@
       <c r="E19" s="11">
         <v>135</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="11">
-        <v>0</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="I19" s="12"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="11">
+        <v>0</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>108</v>
+      </c>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
       <c r="L19" s="12"/>
@@ -12012,13 +12051,14 @@
       <c r="BB19" s="12"/>
       <c r="BC19" s="12"/>
       <c r="BD19" s="12"/>
-    </row>
-    <row r="20" ht="20.25" spans="2:56">
+      <c r="BE19" s="12"/>
+    </row>
+    <row r="20" ht="20.25" spans="2:57">
       <c r="B20" s="11">
         <v>3005005</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D20" s="11">
         <v>7</v>
@@ -12026,16 +12066,16 @@
       <c r="E20" s="11">
         <v>165</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="G20" s="11">
-        <v>0</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I20" s="12"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="11">
+        <v>0</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>110</v>
+      </c>
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
       <c r="L20" s="12"/>
@@ -12083,13 +12123,14 @@
       <c r="BB20" s="12"/>
       <c r="BC20" s="12"/>
       <c r="BD20" s="12"/>
-    </row>
-    <row r="21" ht="20.25" spans="2:56">
+      <c r="BE20" s="12"/>
+    </row>
+    <row r="21" ht="20.25" spans="2:57">
       <c r="B21" s="11">
         <v>3006005</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" s="11">
         <v>7</v>
@@ -12097,16 +12138,16 @@
       <c r="E21" s="11">
         <v>200</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="G21" s="11">
-        <v>0</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="I21" s="12"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>120</v>
+      </c>
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
       <c r="L21" s="12"/>
@@ -12154,13 +12195,14 @@
       <c r="BB21" s="12"/>
       <c r="BC21" s="12"/>
       <c r="BD21" s="12"/>
-    </row>
-    <row r="22" ht="20.25" spans="2:56">
+      <c r="BE21" s="12"/>
+    </row>
+    <row r="22" ht="20.25" spans="2:57">
       <c r="B22" s="11">
         <v>1001006</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D22" s="11">
         <v>7</v>
@@ -12169,15 +12211,17 @@
         <v>10</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="G22" s="11">
+        <v>121</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" s="11">
         <v>10</v>
       </c>
-      <c r="H22" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="I22" s="12"/>
+      <c r="I22" s="11" t="s">
+        <v>123</v>
+      </c>
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
       <c r="L22" s="12"/>
@@ -12225,13 +12269,14 @@
       <c r="BB22" s="12"/>
       <c r="BC22" s="12"/>
       <c r="BD22" s="12"/>
-    </row>
-    <row r="23" ht="20.25" spans="2:56">
+      <c r="BE22" s="12"/>
+    </row>
+    <row r="23" ht="20.25" spans="2:57">
       <c r="B23" s="11">
         <v>1002006</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D23" s="11">
         <v>7</v>
@@ -12239,16 +12284,16 @@
       <c r="E23" s="11">
         <v>35</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" s="11">
+      <c r="F23" s="11"/>
+      <c r="G23" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="11">
         <v>15</v>
       </c>
-      <c r="H23" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="I23" s="12"/>
+      <c r="I23" s="11" t="s">
+        <v>123</v>
+      </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12"/>
       <c r="L23" s="12"/>
@@ -12296,13 +12341,14 @@
       <c r="BB23" s="12"/>
       <c r="BC23" s="12"/>
       <c r="BD23" s="12"/>
-    </row>
-    <row r="24" ht="20.25" spans="2:56">
+      <c r="BE23" s="12"/>
+    </row>
+    <row r="24" ht="20.25" spans="2:57">
       <c r="B24" s="11">
         <v>1003006</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D24" s="11">
         <v>7</v>
@@ -12310,16 +12356,16 @@
       <c r="E24" s="11">
         <v>70</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="G24" s="11">
+      <c r="F24" s="11"/>
+      <c r="G24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H24" s="11">
         <v>20</v>
       </c>
-      <c r="H24" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="I24" s="12"/>
+      <c r="I24" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="J24" s="12"/>
       <c r="K24" s="12"/>
       <c r="L24" s="12"/>
@@ -12367,13 +12413,14 @@
       <c r="BB24" s="12"/>
       <c r="BC24" s="12"/>
       <c r="BD24" s="12"/>
-    </row>
-    <row r="25" ht="20.25" spans="2:56">
+      <c r="BE24" s="12"/>
+    </row>
+    <row r="25" ht="20.25" spans="2:57">
       <c r="B25" s="11">
         <v>1004006</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D25" s="11">
         <v>7</v>
@@ -12381,16 +12428,16 @@
       <c r="E25" s="11">
         <v>135</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G25" s="11">
-        <v>0</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="I25" s="12"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H25" s="11">
+        <v>0</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="J25" s="12"/>
       <c r="K25" s="12"/>
       <c r="L25" s="12"/>
@@ -12438,13 +12485,14 @@
       <c r="BB25" s="12"/>
       <c r="BC25" s="12"/>
       <c r="BD25" s="12"/>
-    </row>
-    <row r="26" ht="20.25" spans="2:56">
+      <c r="BE25" s="12"/>
+    </row>
+    <row r="26" ht="20.25" spans="2:57">
       <c r="B26" s="11">
         <v>1005006</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D26" s="11">
         <v>7</v>
@@ -12452,16 +12500,16 @@
       <c r="E26" s="11">
         <v>165</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="G26" s="11">
-        <v>0</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="I26" s="12"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" s="11">
+        <v>0</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>130</v>
+      </c>
       <c r="J26" s="12"/>
       <c r="K26" s="12"/>
       <c r="L26" s="12"/>
@@ -12509,13 +12557,14 @@
       <c r="BB26" s="12"/>
       <c r="BC26" s="12"/>
       <c r="BD26" s="12"/>
-    </row>
-    <row r="27" ht="20.25" spans="2:56">
+      <c r="BE26" s="12"/>
+    </row>
+    <row r="27" ht="20.25" spans="2:57">
       <c r="B27" s="11">
         <v>1006006</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D27" s="11">
         <v>7</v>
@@ -12523,16 +12572,16 @@
       <c r="E27" s="11">
         <v>200</v>
       </c>
-      <c r="F27" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G27" s="11">
-        <v>0</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="I27" s="12"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>132</v>
+      </c>
       <c r="J27" s="12"/>
       <c r="K27" s="12"/>
       <c r="L27" s="12"/>
@@ -12580,13 +12629,14 @@
       <c r="BB27" s="12"/>
       <c r="BC27" s="12"/>
       <c r="BD27" s="12"/>
-    </row>
-    <row r="28" ht="20.25" spans="2:56">
+      <c r="BE27" s="12"/>
+    </row>
+    <row r="28" ht="20.25" spans="2:57">
       <c r="B28" s="11">
         <v>2001006</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D28" s="11">
         <v>7</v>
@@ -12595,15 +12645,17 @@
         <v>10</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="G28" s="11">
+        <v>133</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H28" s="11">
         <v>10</v>
       </c>
-      <c r="H28" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I28" s="12"/>
+      <c r="I28" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="J28" s="12"/>
       <c r="K28" s="12"/>
       <c r="L28" s="12"/>
@@ -12651,13 +12703,14 @@
       <c r="BB28" s="12"/>
       <c r="BC28" s="12"/>
       <c r="BD28" s="12"/>
-    </row>
-    <row r="29" ht="20.25" spans="2:56">
+      <c r="BE28" s="12"/>
+    </row>
+    <row r="29" ht="20.25" spans="2:57">
       <c r="B29" s="11">
         <v>2002006</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D29" s="11">
         <v>7</v>
@@ -12665,16 +12718,16 @@
       <c r="E29" s="11">
         <v>35</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="G29" s="11">
+      <c r="F29" s="11"/>
+      <c r="G29" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" s="11">
         <v>15</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I29" s="12"/>
+      <c r="I29" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="J29" s="12"/>
       <c r="K29" s="12"/>
       <c r="L29" s="12"/>
@@ -12722,13 +12775,14 @@
       <c r="BB29" s="12"/>
       <c r="BC29" s="12"/>
       <c r="BD29" s="12"/>
-    </row>
-    <row r="30" ht="20.25" spans="2:56">
+      <c r="BE29" s="12"/>
+    </row>
+    <row r="30" ht="20.25" spans="2:57">
       <c r="B30" s="11">
         <v>2003006</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D30" s="11">
         <v>7</v>
@@ -12736,16 +12790,16 @@
       <c r="E30" s="11">
         <v>70</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="G30" s="11">
+      <c r="F30" s="11"/>
+      <c r="G30" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="H30" s="11">
         <v>20</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="I30" s="12"/>
+      <c r="I30" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="J30" s="12"/>
       <c r="K30" s="12"/>
       <c r="L30" s="12"/>
@@ -12793,13 +12847,14 @@
       <c r="BB30" s="12"/>
       <c r="BC30" s="12"/>
       <c r="BD30" s="12"/>
-    </row>
-    <row r="31" ht="20.25" spans="2:56">
+      <c r="BE30" s="12"/>
+    </row>
+    <row r="31" ht="20.25" spans="2:57">
       <c r="B31" s="11">
         <v>2004006</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D31" s="11">
         <v>7</v>
@@ -12807,16 +12862,16 @@
       <c r="E31" s="11">
         <v>135</v>
       </c>
-      <c r="F31" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G31" s="11">
-        <v>0</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="I31" s="12"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="H31" s="11">
+        <v>0</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="J31" s="12"/>
       <c r="K31" s="12"/>
       <c r="L31" s="12"/>
@@ -12864,13 +12919,14 @@
       <c r="BB31" s="12"/>
       <c r="BC31" s="12"/>
       <c r="BD31" s="12"/>
-    </row>
-    <row r="32" ht="20.25" spans="2:56">
+      <c r="BE31" s="12"/>
+    </row>
+    <row r="32" ht="20.25" spans="2:57">
       <c r="B32" s="11">
         <v>2005006</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D32" s="11">
         <v>7</v>
@@ -12878,16 +12934,16 @@
       <c r="E32" s="11">
         <v>165</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" s="11">
-        <v>0</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="I32" s="12"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="H32" s="11">
+        <v>0</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>141</v>
+      </c>
       <c r="J32" s="12"/>
       <c r="K32" s="12"/>
       <c r="L32" s="12"/>
@@ -12935,13 +12991,14 @@
       <c r="BB32" s="12"/>
       <c r="BC32" s="12"/>
       <c r="BD32" s="12"/>
-    </row>
-    <row r="33" ht="20.25" spans="2:56">
+      <c r="BE32" s="12"/>
+    </row>
+    <row r="33" ht="20.25" spans="2:57">
       <c r="B33" s="11">
         <v>2006006</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D33" s="11">
         <v>7</v>
@@ -12949,16 +13006,16 @@
       <c r="E33" s="11">
         <v>200</v>
       </c>
-      <c r="F33" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="G33" s="11">
-        <v>0</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="I33" s="12"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="H33" s="11">
+        <v>0</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>143</v>
+      </c>
       <c r="J33" s="12"/>
       <c r="K33" s="12"/>
       <c r="L33" s="12"/>
@@ -13006,13 +13063,14 @@
       <c r="BB33" s="12"/>
       <c r="BC33" s="12"/>
       <c r="BD33" s="12"/>
-    </row>
-    <row r="34" ht="20.25" spans="2:56">
+      <c r="BE33" s="12"/>
+    </row>
+    <row r="34" ht="20.25" spans="2:57">
       <c r="B34" s="11">
         <v>3001006</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D34" s="11">
         <v>7</v>
@@ -13021,15 +13079,17 @@
         <v>10</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="G34" s="11">
+        <v>144</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H34" s="11">
         <v>10</v>
       </c>
-      <c r="H34" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I34" s="12"/>
+      <c r="I34" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="J34" s="12"/>
       <c r="K34" s="12"/>
       <c r="L34" s="12"/>
@@ -13077,13 +13137,14 @@
       <c r="BB34" s="12"/>
       <c r="BC34" s="12"/>
       <c r="BD34" s="12"/>
-    </row>
-    <row r="35" ht="20.25" spans="2:56">
+      <c r="BE34" s="12"/>
+    </row>
+    <row r="35" ht="20.25" spans="2:57">
       <c r="B35" s="11">
         <v>3002006</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D35" s="11">
         <v>7</v>
@@ -13091,16 +13152,16 @@
       <c r="E35" s="11">
         <v>35</v>
       </c>
-      <c r="F35" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="G35" s="11">
+      <c r="F35" s="11"/>
+      <c r="G35" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="H35" s="11">
         <v>15</v>
       </c>
-      <c r="H35" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I35" s="12"/>
+      <c r="I35" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="J35" s="12"/>
       <c r="K35" s="12"/>
       <c r="L35" s="12"/>
@@ -13148,13 +13209,14 @@
       <c r="BB35" s="12"/>
       <c r="BC35" s="12"/>
       <c r="BD35" s="12"/>
-    </row>
-    <row r="36" ht="20.25" spans="2:56">
+      <c r="BE35" s="12"/>
+    </row>
+    <row r="36" ht="20.25" spans="2:57">
       <c r="B36" s="11">
         <v>3003006</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D36" s="11">
         <v>7</v>
@@ -13162,16 +13224,16 @@
       <c r="E36" s="11">
         <v>70</v>
       </c>
-      <c r="F36" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="G36" s="11">
+      <c r="F36" s="11"/>
+      <c r="G36" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="H36" s="11">
         <v>20</v>
       </c>
-      <c r="H36" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="I36" s="12"/>
+      <c r="I36" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="J36" s="12"/>
       <c r="K36" s="12"/>
       <c r="L36" s="12"/>
@@ -13219,13 +13281,14 @@
       <c r="BB36" s="12"/>
       <c r="BC36" s="12"/>
       <c r="BD36" s="12"/>
-    </row>
-    <row r="37" ht="20.25" spans="2:56">
+      <c r="BE36" s="12"/>
+    </row>
+    <row r="37" ht="20.25" spans="2:57">
       <c r="B37" s="11">
         <v>3004006</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D37" s="11">
         <v>7</v>
@@ -13233,16 +13296,16 @@
       <c r="E37" s="11">
         <v>135</v>
       </c>
-      <c r="F37" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G37" s="11">
-        <v>0</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="I37" s="12"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="H37" s="11">
+        <v>0</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>145</v>
+      </c>
       <c r="J37" s="12"/>
       <c r="K37" s="12"/>
       <c r="L37" s="12"/>
@@ -13290,13 +13353,14 @@
       <c r="BB37" s="12"/>
       <c r="BC37" s="12"/>
       <c r="BD37" s="12"/>
-    </row>
-    <row r="38" ht="20.25" spans="2:56">
+      <c r="BE37" s="12"/>
+    </row>
+    <row r="38" ht="20.25" spans="2:57">
       <c r="B38" s="11">
         <v>3005006</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D38" s="11">
         <v>7</v>
@@ -13304,16 +13368,16 @@
       <c r="E38" s="11">
         <v>165</v>
       </c>
-      <c r="F38" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="G38" s="11">
-        <v>0</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="I38" s="12"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="H38" s="11">
+        <v>0</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>141</v>
+      </c>
       <c r="J38" s="12"/>
       <c r="K38" s="12"/>
       <c r="L38" s="12"/>
@@ -13361,13 +13425,14 @@
       <c r="BB38" s="12"/>
       <c r="BC38" s="12"/>
       <c r="BD38" s="12"/>
-    </row>
-    <row r="39" ht="20.25" spans="2:56">
+      <c r="BE38" s="12"/>
+    </row>
+    <row r="39" ht="20.25" spans="2:57">
       <c r="B39" s="11">
         <v>3006006</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D39" s="11">
         <v>7</v>
@@ -13375,16 +13440,16 @@
       <c r="E39" s="11">
         <v>200</v>
       </c>
-      <c r="F39" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G39" s="11">
-        <v>0</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="I39" s="12"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="H39" s="11">
+        <v>0</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="J39" s="12"/>
       <c r="K39" s="12"/>
       <c r="L39" s="12"/>
@@ -13432,13 +13497,14 @@
       <c r="BB39" s="12"/>
       <c r="BC39" s="12"/>
       <c r="BD39" s="12"/>
-    </row>
-    <row r="40" ht="20.25" spans="2:56">
+      <c r="BE39" s="12"/>
+    </row>
+    <row r="40" ht="20.25" spans="2:57">
       <c r="B40" s="11">
         <v>1001007</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D40" s="11">
         <v>7</v>
@@ -13447,15 +13513,17 @@
         <v>10</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G40" s="11">
+        <v>149</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="H40" s="11">
         <v>10</v>
       </c>
-      <c r="H40" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="I40" s="12"/>
+      <c r="I40" s="11" t="s">
+        <v>150</v>
+      </c>
       <c r="J40" s="12"/>
       <c r="K40" s="12"/>
       <c r="L40" s="12"/>
@@ -13503,13 +13571,14 @@
       <c r="BB40" s="12"/>
       <c r="BC40" s="12"/>
       <c r="BD40" s="12"/>
-    </row>
-    <row r="41" ht="20.25" spans="2:56">
+      <c r="BE40" s="12"/>
+    </row>
+    <row r="41" ht="20.25" spans="2:57">
       <c r="B41" s="11">
         <v>1002007</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D41" s="11">
         <v>7</v>
@@ -13517,16 +13586,16 @@
       <c r="E41" s="11">
         <v>35</v>
       </c>
-      <c r="F41" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="G41" s="11">
+      <c r="F41" s="11"/>
+      <c r="G41" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="H41" s="11">
         <v>15</v>
       </c>
-      <c r="H41" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="I41" s="12"/>
+      <c r="I41" s="11" t="s">
+        <v>150</v>
+      </c>
       <c r="J41" s="12"/>
       <c r="K41" s="12"/>
       <c r="L41" s="12"/>
@@ -13574,13 +13643,14 @@
       <c r="BB41" s="12"/>
       <c r="BC41" s="12"/>
       <c r="BD41" s="12"/>
-    </row>
-    <row r="42" ht="20.25" spans="2:56">
+      <c r="BE41" s="12"/>
+    </row>
+    <row r="42" ht="20.25" spans="2:57">
       <c r="B42" s="11">
         <v>1003007</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D42" s="11">
         <v>7</v>
@@ -13588,16 +13658,16 @@
       <c r="E42" s="11">
         <v>70</v>
       </c>
-      <c r="F42" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G42" s="11">
+      <c r="F42" s="11"/>
+      <c r="G42" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="H42" s="11">
         <v>20</v>
       </c>
-      <c r="H42" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="I42" s="12"/>
+      <c r="I42" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="J42" s="12"/>
       <c r="K42" s="12"/>
       <c r="L42" s="12"/>
@@ -13645,13 +13715,14 @@
       <c r="BB42" s="12"/>
       <c r="BC42" s="12"/>
       <c r="BD42" s="12"/>
-    </row>
-    <row r="43" ht="20.25" spans="2:56">
+      <c r="BE42" s="12"/>
+    </row>
+    <row r="43" ht="20.25" spans="2:57">
       <c r="B43" s="11">
         <v>1004007</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D43" s="11">
         <v>7</v>
@@ -13659,16 +13730,16 @@
       <c r="E43" s="11">
         <v>135</v>
       </c>
-      <c r="F43" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="G43" s="11">
-        <v>0</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="I43" s="12"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H43" s="11">
+        <v>0</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="J43" s="12"/>
       <c r="K43" s="12"/>
       <c r="L43" s="12"/>
@@ -13716,13 +13787,14 @@
       <c r="BB43" s="12"/>
       <c r="BC43" s="12"/>
       <c r="BD43" s="12"/>
-    </row>
-    <row r="44" ht="20.25" spans="2:56">
+      <c r="BE43" s="12"/>
+    </row>
+    <row r="44" ht="20.25" spans="2:57">
       <c r="B44" s="11">
         <v>1005007</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D44" s="11">
         <v>7</v>
@@ -13730,16 +13802,16 @@
       <c r="E44" s="11">
         <v>165</v>
       </c>
-      <c r="F44" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="G44" s="11">
-        <v>0</v>
-      </c>
-      <c r="H44" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="I44" s="12"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="H44" s="11">
+        <v>0</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="J44" s="12"/>
       <c r="K44" s="12"/>
       <c r="L44" s="12"/>
@@ -13787,13 +13859,14 @@
       <c r="BB44" s="12"/>
       <c r="BC44" s="12"/>
       <c r="BD44" s="12"/>
-    </row>
-    <row r="45" ht="20.25" spans="2:56">
+      <c r="BE44" s="12"/>
+    </row>
+    <row r="45" ht="20.25" spans="2:57">
       <c r="B45" s="11">
         <v>1006007</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D45" s="11">
         <v>7</v>
@@ -13801,16 +13874,16 @@
       <c r="E45" s="11">
         <v>200</v>
       </c>
-      <c r="F45" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="G45" s="11">
-        <v>0</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="I45" s="12"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H45" s="11">
+        <v>0</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>141</v>
+      </c>
       <c r="J45" s="12"/>
       <c r="K45" s="12"/>
       <c r="L45" s="12"/>
@@ -13858,13 +13931,14 @@
       <c r="BB45" s="12"/>
       <c r="BC45" s="12"/>
       <c r="BD45" s="12"/>
-    </row>
-    <row r="46" ht="20.25" spans="2:56">
+      <c r="BE45" s="12"/>
+    </row>
+    <row r="46" ht="20.25" spans="2:57">
       <c r="B46" s="11">
         <v>2001007</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D46" s="11">
         <v>7</v>
@@ -13873,15 +13947,17 @@
         <v>10</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G46" s="11">
+        <v>154</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="H46" s="11">
         <v>10</v>
       </c>
-      <c r="H46" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="I46" s="12"/>
+      <c r="I46" s="11" t="s">
+        <v>156</v>
+      </c>
       <c r="J46" s="12"/>
       <c r="K46" s="12"/>
       <c r="L46" s="12"/>
@@ -13929,13 +14005,14 @@
       <c r="BB46" s="12"/>
       <c r="BC46" s="12"/>
       <c r="BD46" s="12"/>
-    </row>
-    <row r="47" ht="20.25" spans="2:56">
+      <c r="BE46" s="12"/>
+    </row>
+    <row r="47" ht="20.25" spans="2:57">
       <c r="B47" s="11">
         <v>2002007</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D47" s="11">
         <v>7</v>
@@ -13943,16 +14020,16 @@
       <c r="E47" s="11">
         <v>35</v>
       </c>
-      <c r="F47" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="G47" s="11">
+      <c r="F47" s="11"/>
+      <c r="G47" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="H47" s="11">
         <v>15</v>
       </c>
-      <c r="H47" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="I47" s="12"/>
+      <c r="I47" s="11" t="s">
+        <v>156</v>
+      </c>
       <c r="J47" s="12"/>
       <c r="K47" s="12"/>
       <c r="L47" s="12"/>
@@ -14000,13 +14077,14 @@
       <c r="BB47" s="12"/>
       <c r="BC47" s="12"/>
       <c r="BD47" s="12"/>
-    </row>
-    <row r="48" ht="20.25" spans="2:56">
+      <c r="BE47" s="12"/>
+    </row>
+    <row r="48" ht="20.25" spans="2:57">
       <c r="B48" s="11">
         <v>2003007</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D48" s="11">
         <v>7</v>
@@ -14014,16 +14092,16 @@
       <c r="E48" s="11">
         <v>70</v>
       </c>
-      <c r="F48" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="G48" s="11">
+      <c r="F48" s="11"/>
+      <c r="G48" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H48" s="11">
         <v>20</v>
       </c>
-      <c r="H48" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="I48" s="12"/>
+      <c r="I48" s="11" t="s">
+        <v>123</v>
+      </c>
       <c r="J48" s="12"/>
       <c r="K48" s="12"/>
       <c r="L48" s="12"/>
@@ -14071,13 +14149,14 @@
       <c r="BB48" s="12"/>
       <c r="BC48" s="12"/>
       <c r="BD48" s="12"/>
-    </row>
-    <row r="49" ht="20.25" spans="2:56">
+      <c r="BE48" s="12"/>
+    </row>
+    <row r="49" ht="20.25" spans="2:57">
       <c r="B49" s="11">
         <v>2004007</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D49" s="11">
         <v>7</v>
@@ -14085,16 +14164,16 @@
       <c r="E49" s="11">
         <v>135</v>
       </c>
-      <c r="F49" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="G49" s="11">
-        <v>0</v>
-      </c>
-      <c r="H49" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="I49" s="12"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="H49" s="11">
+        <v>0</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>160</v>
+      </c>
       <c r="J49" s="12"/>
       <c r="K49" s="12"/>
       <c r="L49" s="12"/>
@@ -14142,13 +14221,14 @@
       <c r="BB49" s="12"/>
       <c r="BC49" s="12"/>
       <c r="BD49" s="12"/>
-    </row>
-    <row r="50" ht="20.25" spans="2:56">
+      <c r="BE49" s="12"/>
+    </row>
+    <row r="50" ht="20.25" spans="2:57">
       <c r="B50" s="11">
         <v>2005007</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D50" s="11">
         <v>7</v>
@@ -14156,16 +14236,16 @@
       <c r="E50" s="11">
         <v>165</v>
       </c>
-      <c r="F50" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="G50" s="11">
-        <v>0</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="I50" s="12"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="H50" s="11">
+        <v>0</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>162</v>
+      </c>
       <c r="J50" s="12"/>
       <c r="K50" s="12"/>
       <c r="L50" s="12"/>
@@ -14213,13 +14293,14 @@
       <c r="BB50" s="12"/>
       <c r="BC50" s="12"/>
       <c r="BD50" s="12"/>
-    </row>
-    <row r="51" ht="20.25" spans="2:56">
+      <c r="BE50" s="12"/>
+    </row>
+    <row r="51" ht="20.25" spans="2:57">
       <c r="B51" s="11">
         <v>2006007</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D51" s="11">
         <v>7</v>
@@ -14227,16 +14308,16 @@
       <c r="E51" s="11">
         <v>200</v>
       </c>
-      <c r="F51" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="G51" s="11">
-        <v>0</v>
-      </c>
-      <c r="H51" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="I51" s="12"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="H51" s="11">
+        <v>0</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>164</v>
+      </c>
       <c r="J51" s="12"/>
       <c r="K51" s="12"/>
       <c r="L51" s="12"/>
@@ -14284,13 +14365,14 @@
       <c r="BB51" s="12"/>
       <c r="BC51" s="12"/>
       <c r="BD51" s="12"/>
-    </row>
-    <row r="52" ht="20.25" spans="2:56">
+      <c r="BE51" s="12"/>
+    </row>
+    <row r="52" ht="20.25" spans="2:57">
       <c r="B52" s="11">
         <v>3001007</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D52" s="11">
         <v>7</v>
@@ -14299,15 +14381,17 @@
         <v>10</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="G52" s="11">
+        <v>144</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="H52" s="11">
         <v>10</v>
       </c>
-      <c r="H52" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I52" s="12"/>
+      <c r="I52" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="J52" s="12"/>
       <c r="K52" s="12"/>
       <c r="L52" s="12"/>
@@ -14355,13 +14439,14 @@
       <c r="BB52" s="12"/>
       <c r="BC52" s="12"/>
       <c r="BD52" s="12"/>
-    </row>
-    <row r="53" ht="20.25" spans="2:56">
+      <c r="BE52" s="12"/>
+    </row>
+    <row r="53" ht="20.25" spans="2:57">
       <c r="B53" s="11">
         <v>3002007</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D53" s="11">
         <v>7</v>
@@ -14369,16 +14454,16 @@
       <c r="E53" s="11">
         <v>35</v>
       </c>
-      <c r="F53" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G53" s="11">
+      <c r="F53" s="11"/>
+      <c r="G53" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="H53" s="11">
         <v>15</v>
       </c>
-      <c r="H53" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I53" s="12"/>
+      <c r="I53" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="J53" s="12"/>
       <c r="K53" s="12"/>
       <c r="L53" s="12"/>
@@ -14426,13 +14511,14 @@
       <c r="BB53" s="12"/>
       <c r="BC53" s="12"/>
       <c r="BD53" s="12"/>
-    </row>
-    <row r="54" ht="20.25" spans="2:56">
+      <c r="BE53" s="12"/>
+    </row>
+    <row r="54" ht="20.25" spans="2:57">
       <c r="B54" s="11">
         <v>3003007</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D54" s="11">
         <v>7</v>
@@ -14440,16 +14526,16 @@
       <c r="E54" s="11">
         <v>70</v>
       </c>
-      <c r="F54" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="G54" s="11">
+      <c r="F54" s="11"/>
+      <c r="G54" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="H54" s="11">
         <v>20</v>
       </c>
-      <c r="H54" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="I54" s="12"/>
+      <c r="I54" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="J54" s="12"/>
       <c r="K54" s="12"/>
       <c r="L54" s="12"/>
@@ -14497,13 +14583,14 @@
       <c r="BB54" s="12"/>
       <c r="BC54" s="12"/>
       <c r="BD54" s="12"/>
-    </row>
-    <row r="55" ht="20.25" spans="2:56">
+      <c r="BE54" s="12"/>
+    </row>
+    <row r="55" ht="20.25" spans="2:57">
       <c r="B55" s="11">
         <v>3004007</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D55" s="11">
         <v>7</v>
@@ -14511,16 +14598,16 @@
       <c r="E55" s="11">
         <v>135</v>
       </c>
-      <c r="F55" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="G55" s="11">
-        <v>0</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="I55" s="12"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H55" s="11">
+        <v>0</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>145</v>
+      </c>
       <c r="J55" s="12"/>
       <c r="K55" s="12"/>
       <c r="L55" s="12"/>
@@ -14568,13 +14655,14 @@
       <c r="BB55" s="12"/>
       <c r="BC55" s="12"/>
       <c r="BD55" s="12"/>
-    </row>
-    <row r="56" ht="20.25" spans="2:56">
+      <c r="BE55" s="12"/>
+    </row>
+    <row r="56" ht="20.25" spans="2:57">
       <c r="B56" s="11">
         <v>3005007</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D56" s="11">
         <v>7</v>
@@ -14582,16 +14670,16 @@
       <c r="E56" s="11">
         <v>165</v>
       </c>
-      <c r="F56" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="G56" s="11">
-        <v>0</v>
-      </c>
-      <c r="H56" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="I56" s="12"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="H56" s="11">
+        <v>0</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>141</v>
+      </c>
       <c r="J56" s="12"/>
       <c r="K56" s="12"/>
       <c r="L56" s="12"/>
@@ -14639,13 +14727,14 @@
       <c r="BB56" s="12"/>
       <c r="BC56" s="12"/>
       <c r="BD56" s="12"/>
-    </row>
-    <row r="57" ht="20.25" spans="2:56">
+      <c r="BE56" s="12"/>
+    </row>
+    <row r="57" ht="20.25" spans="2:57">
       <c r="B57" s="11">
         <v>3006007</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D57" s="11">
         <v>7</v>
@@ -14653,14 +14742,15 @@
       <c r="E57" s="11">
         <v>200</v>
       </c>
-      <c r="F57" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="G57" s="11">
-        <v>0</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>141</v>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="H57" s="11">
+        <v>0</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
